--- a/data hasil olah program pempar.xlsx
+++ b/data hasil olah program pempar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\semester 4\PemPar\tugas\projek uts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6575EFED-0C97-47A3-990F-56F5EC36D455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9325618F-86FC-46C8-957C-7441289FFA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="21795" windowHeight="12975" xr2:uid="{1BEBE3C8-2623-48D9-9188-AE9F45C8624C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{1BEBE3C8-2623-48D9-9188-AE9F45C8624C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="13">
   <si>
     <t>hasil ke-1</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>12D</t>
-  </si>
-  <si>
-    <t>3D</t>
   </si>
 </sst>
 </file>
@@ -1662,6 +1659,1461 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID"/>
+              <a:t>Perbandingan</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ID" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ID"/>
+              <a:t>Variasi Jumlah Data</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ID" baseline="0"/>
+              <a:t> Terhadap 10 Prosesor</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-ID"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$AC$20:$AC$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AD$20:$AD$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0.29360000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6677</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3167</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.4384</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28.62</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>48.0702</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74.829599999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115.0543</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>170.99</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>275.3211</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-731E-4DBC-ADBC-AD36AE85D210}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1820034816"/>
+        <c:axId val="1820035296"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1820034816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2000"/>
+          <c:min val="200"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Jumlah Data</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1820035296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1820035296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Waktu (detik)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1820034816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Perbandingan Variasi Jumlah Prosesor Terhadap 1000 Data</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$AF$20:$AF$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AG$20:$AG$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>57.712000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.1297</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31.456299999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.9282</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46.3705</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34.328299999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.576999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70.465400000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93.371200000000002</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>119.9444</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7095-4B30-A026-7941D413554F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1728134128"/>
+        <c:axId val="1728133648"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1728134128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="22"/>
+          <c:min val="4"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Jumlah Prosesor</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1728133648"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1728133648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Waktu (detik)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1728134128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-ID" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="44546A"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Perbandingan Variasi Jumlah Dimensi Terhadap 10 Prosesor dan 1000 Data</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$AI$20:$AI$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AJ$20:$AJ$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>31.9282</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.5197</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.2225</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31.254200000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31.569500000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32.386000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>32.926499999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.115000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35.5867</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>35.345300000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A5F8-466E-BC0C-4CF5C6F754C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="96866160"/>
+        <c:axId val="96866640"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="96866160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="12"/>
+          <c:min val="3"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Jumlah Dimensi</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="96866640"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="96866640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-ID"/>
+                  <a:t>Waktu (detik)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="40000"/>
+                <a:lumOff val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="96866160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1742,6 +3194,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -2770,6 +4342,1443 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="242">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2843,6 +5852,114 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>26193</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>54768</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{513CF574-B1DC-9F8E-0C86-8DF435443D43}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>373855</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>254793</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E825DF8D-E73F-F27C-825C-473D526FE7E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>445294</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>483394</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5688BD20-3136-0456-75F4-5953D154CD54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4234,19 +7351,19 @@
       <c r="AC20" s="9">
         <v>200</v>
       </c>
-      <c r="AD20" s="6">
+      <c r="AD20" s="7">
         <v>0.29360000000000003</v>
       </c>
       <c r="AF20" s="2">
         <v>4</v>
       </c>
-      <c r="AG20" s="6">
+      <c r="AG20" s="7">
         <v>57.712000000000003</v>
       </c>
-      <c r="AI20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AJ20" s="6">
+      <c r="AI20" s="2">
+        <v>3</v>
+      </c>
+      <c r="AJ20" s="7">
         <v>31.9282</v>
       </c>
     </row>
@@ -4303,19 +7420,19 @@
       <c r="AC21" s="9">
         <v>400</v>
       </c>
-      <c r="AD21" s="6">
+      <c r="AD21" s="7">
         <v>2.6677</v>
       </c>
       <c r="AF21" s="2">
         <v>6</v>
       </c>
-      <c r="AG21" s="6">
+      <c r="AG21" s="7">
         <v>29.1297</v>
       </c>
-      <c r="AI21" s="2" t="s">
+      <c r="AI21" s="2">
         <v>4</v>
       </c>
-      <c r="AJ21" s="6">
+      <c r="AJ21" s="7">
         <v>29.5197</v>
       </c>
     </row>
@@ -4375,19 +7492,19 @@
       <c r="AC22" s="9">
         <v>600</v>
       </c>
-      <c r="AD22" s="6">
+      <c r="AD22" s="7">
         <v>7.3167</v>
       </c>
       <c r="AF22" s="2">
         <v>8</v>
       </c>
-      <c r="AG22" s="6">
+      <c r="AG22" s="7">
         <v>31.456299999999999</v>
       </c>
-      <c r="AI22" s="2" t="s">
+      <c r="AI22" s="2">
         <v>5</v>
       </c>
-      <c r="AJ22" s="6">
+      <c r="AJ22" s="7">
         <v>30.2225</v>
       </c>
     </row>
@@ -4452,19 +7569,19 @@
       <c r="AC23" s="9">
         <v>800</v>
       </c>
-      <c r="AD23" s="6">
+      <c r="AD23" s="7">
         <v>15.4384</v>
       </c>
       <c r="AF23" s="9">
         <v>10</v>
       </c>
-      <c r="AG23" s="6">
+      <c r="AG23" s="7">
         <v>31.9282</v>
       </c>
-      <c r="AI23" s="2" t="s">
+      <c r="AI23" s="2">
         <v>6</v>
       </c>
-      <c r="AJ23" s="6">
+      <c r="AJ23" s="7">
         <v>31.254200000000001</v>
       </c>
     </row>
@@ -4529,19 +7646,19 @@
       <c r="AC24" s="9">
         <v>1000</v>
       </c>
-      <c r="AD24" s="6">
+      <c r="AD24" s="7">
         <v>28.62</v>
       </c>
       <c r="AF24" s="2">
         <v>12</v>
       </c>
-      <c r="AG24" s="6">
+      <c r="AG24" s="7">
         <v>46.3705</v>
       </c>
-      <c r="AI24" s="2" t="s">
+      <c r="AI24" s="2">
         <v>7</v>
       </c>
-      <c r="AJ24" s="6">
+      <c r="AJ24" s="7">
         <v>31.569500000000001</v>
       </c>
     </row>
@@ -4607,19 +7724,19 @@
       <c r="AC25" s="9">
         <v>1200</v>
       </c>
-      <c r="AD25" s="6">
+      <c r="AD25" s="7">
         <v>48.0702</v>
       </c>
       <c r="AF25" s="2">
         <v>14</v>
       </c>
-      <c r="AG25" s="6">
+      <c r="AG25" s="7">
         <v>34.328299999999999</v>
       </c>
-      <c r="AI25" s="2" t="s">
+      <c r="AI25" s="2">
         <v>8</v>
       </c>
-      <c r="AJ25" s="6">
+      <c r="AJ25" s="7">
         <v>32.386000000000003</v>
       </c>
     </row>
@@ -4684,19 +7801,19 @@
       <c r="AC26" s="9">
         <v>1400</v>
       </c>
-      <c r="AD26" s="6">
+      <c r="AD26" s="7">
         <v>74.829599999999999</v>
       </c>
       <c r="AF26" s="2">
         <v>16</v>
       </c>
-      <c r="AG26" s="6">
+      <c r="AG26" s="7">
         <v>48.576999999999998</v>
       </c>
-      <c r="AI26" s="2" t="s">
+      <c r="AI26" s="2">
         <v>9</v>
       </c>
-      <c r="AJ26" s="6">
+      <c r="AJ26" s="7">
         <v>32.926499999999997</v>
       </c>
     </row>
@@ -4761,19 +7878,19 @@
       <c r="AC27" s="9">
         <v>1600</v>
       </c>
-      <c r="AD27" s="6">
+      <c r="AD27" s="7">
         <v>115.0543</v>
       </c>
       <c r="AF27" s="2">
         <v>18</v>
       </c>
-      <c r="AG27" s="6">
+      <c r="AG27" s="7">
         <v>70.465400000000002</v>
       </c>
-      <c r="AI27" s="2" t="s">
+      <c r="AI27" s="2">
         <v>10</v>
       </c>
-      <c r="AJ27" s="6">
+      <c r="AJ27" s="7">
         <v>36.115000000000002</v>
       </c>
     </row>
@@ -4815,19 +7932,19 @@
       <c r="AC28" s="9">
         <v>1800</v>
       </c>
-      <c r="AD28" s="6">
+      <c r="AD28" s="7">
         <v>170.99</v>
       </c>
       <c r="AF28" s="2">
         <v>20</v>
       </c>
-      <c r="AG28" s="6">
+      <c r="AG28" s="7">
         <v>93.371200000000002</v>
       </c>
-      <c r="AI28" s="2" t="s">
+      <c r="AI28" s="2">
         <v>11</v>
       </c>
-      <c r="AJ28" s="6">
+      <c r="AJ28" s="7">
         <v>35.5867</v>
       </c>
     </row>
@@ -4869,19 +7986,19 @@
       <c r="AC29" s="9">
         <v>2000</v>
       </c>
-      <c r="AD29" s="6">
+      <c r="AD29" s="7">
         <v>275.3211</v>
       </c>
       <c r="AF29" s="2">
         <v>22</v>
       </c>
-      <c r="AG29" s="6">
+      <c r="AG29" s="7">
         <v>119.9444</v>
       </c>
-      <c r="AI29" s="2" t="s">
+      <c r="AI29" s="2">
         <v>12</v>
       </c>
-      <c r="AJ29" s="6">
+      <c r="AJ29" s="7">
         <v>35.345300000000002</v>
       </c>
     </row>
@@ -5014,12 +8131,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AK5:AK9"/>
-    <mergeCell ref="U20:U29"/>
-    <mergeCell ref="V5:V9"/>
-    <mergeCell ref="V11:V15"/>
-    <mergeCell ref="AC5:AC9"/>
-    <mergeCell ref="AC11:AC15"/>
     <mergeCell ref="H5:H9"/>
     <mergeCell ref="N20:S20"/>
     <mergeCell ref="G33:G34"/>
@@ -5035,6 +8146,12 @@
     <mergeCell ref="F33:F34"/>
     <mergeCell ref="O5:O9"/>
     <mergeCell ref="O11:O15"/>
+    <mergeCell ref="AK5:AK9"/>
+    <mergeCell ref="U20:U29"/>
+    <mergeCell ref="V5:V9"/>
+    <mergeCell ref="V11:V15"/>
+    <mergeCell ref="AC5:AC9"/>
+    <mergeCell ref="AC11:AC15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
